--- a/nr-update-eu-dep/ig/StructureDefinition-fr-core-contact-point.xlsx
+++ b/nr-update-eu-dep/ig/StructureDefinition-fr-core-contact-point.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T07:13:11+00:00</t>
+    <t>2026-05-27T07:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-eu-dep/ig/StructureDefinition-fr-core-contact-point.xlsx
+++ b/nr-update-eu-dep/ig/StructureDefinition-fr-core-contact-point.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T07:23:03+00:00</t>
+    <t>2026-05-27T11:54:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-eu-dep/ig/StructureDefinition-fr-core-contact-point.xlsx
+++ b/nr-update-eu-dep/ig/StructureDefinition-fr-core-contact-point.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T11:54:54+00:00</t>
+    <t>2026-05-27T14:56:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-eu-dep/ig/StructureDefinition-fr-core-contact-point.xlsx
+++ b/nr-update-eu-dep/ig/StructureDefinition-fr-core-contact-point.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:56:15+00:00</t>
+    <t>2026-06-01T09:11:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-eu-dep/ig/StructureDefinition-fr-core-contact-point.xlsx
+++ b/nr-update-eu-dep/ig/StructureDefinition-fr-core-contact-point.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T09:11:05+00:00</t>
+    <t>2026-06-11T14:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
